--- a/GATEWAY/A1#111PASERCONSULTINGXX/PaSer_Consulting_Group/WinPreGest/1.0.0/accreditamento-checklist_V8.2.7.xlsx
+++ b/GATEWAY/A1#111PASERCONSULTINGXX/PaSer_Consulting_Group/WinPreGest/1.0.0/accreditamento-checklist_V8.2.7.xlsx
@@ -1468,13 +1468,13 @@
 Il Documento CDA2 Referto Specialistica Ambulatoriale dovrà essere composto in modo da risultare valido dal punto di vista sintattico, semantico, terminologico. I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso dalla sezione "CASO DI TEST 24" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_OK" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-03-12T09:07:00Z </t>
-  </si>
-  <si>
-    <t xml:space="preserve">c776a9bfde711f4e60a64fe67506a121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16.840.1.113883.2.9.2.9999.1.e2481354423fb42bfe0e5ccbcc56b85713f3f9eb882be0326314ac7d0a452ce3.19a60f7f6b^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t xml:space="preserve">2026-03-17T18:36:00Z </t>
+  </si>
+  <si>
+    <t xml:space="preserve">c3cb1790c985cf3429d83dfea84865c6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16.840.1.113883.2.9.2.9999.1.fa7401d4f3cfff0f43f763829522b91f1b908030881f8ed8262690caff2f096d.5b86d7a63f^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t xml:space="preserve">Nessuna gestione errore richiesta – documento valido </t>
@@ -1490,13 +1490,13 @@
 Il Documento CDA2 Referto Specialistica Ambulatoriale dovrà essere composto in modo da risultare valido dal punto di vista sintattico, semantico, terminologico. I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso dalla sezione "CASO DI TEST 25" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_OK" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-03-12T09:08:00Z </t>
-  </si>
-  <si>
-    <t xml:space="preserve">f86f41af2ba07b96b59219cf9c5ecbeb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16.840.1.113883.2.9.2.9999.1.d2caf1516def2960af3ac25b95881d0d30fd8575c5684441ef3137707e7c16b6.ff94171dca^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t xml:space="preserve">2026-03-17T18:55:00Z </t>
+  </si>
+  <si>
+    <t xml:space="preserve">42eb308576d775d29bbf70af68b8447d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16.840.1.113883.2.9.2.9999.1.fd8f5b9b9f88a84af08a1139870cecd7a69e70e991056b2d06d5c4709bebeec0.65b7e5771d^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t xml:space="preserve">VALIDAZIONE_CDA2_LDO_CT17</t>
@@ -1829,7 +1829,7 @@
     <numFmt numFmtId="166" formatCode="d/m/yyyy"/>
     <numFmt numFmtId="167" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1934,12 +1934,6 @@
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2143,7 +2137,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="63">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2316,19 +2310,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2342,10 +2336,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -2364,7 +2354,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4331,7 +4321,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="42.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="98.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="30" t="n">
         <v>32</v>
       </c>
@@ -4389,7 +4379,7 @@
         <v>71</v>
       </c>
       <c r="U15" s="35"/>
-      <c r="V15" s="43" t="s">
+      <c r="V15" s="41" t="s">
         <v>72</v>
       </c>
       <c r="W15" s="34" t="s">
@@ -4655,7 +4645,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="42.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="98.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="30" t="n">
         <v>40</v>
       </c>
@@ -4677,7 +4667,7 @@
       <c r="G23" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="H23" s="44" t="s">
+      <c r="H23" s="43" t="s">
         <v>86</v>
       </c>
       <c r="I23" s="33" t="s">
@@ -4987,7 +4977,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="42.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="66.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="30" t="n">
         <v>48</v>
       </c>
@@ -10002,7 +9992,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="42.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="164" customFormat="false" ht="86.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="30" t="n">
         <v>448</v>
       </c>
@@ -10019,9 +10009,9 @@
         <v>365</v>
       </c>
       <c r="F164" s="33" t="n">
-        <v>46093</v>
-      </c>
-      <c r="G164" s="45" t="s">
+        <v>46098</v>
+      </c>
+      <c r="G164" s="44" t="s">
         <v>366</v>
       </c>
       <c r="H164" s="40" t="s">
@@ -10065,7 +10055,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="165" customFormat="false" ht="59.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="165" customFormat="false" ht="87.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="30" t="n">
         <v>449</v>
       </c>
@@ -10082,15 +10072,15 @@
         <v>372</v>
       </c>
       <c r="F165" s="33" t="n">
-        <v>46093</v>
-      </c>
-      <c r="G165" s="45" t="s">
+        <v>46098</v>
+      </c>
+      <c r="G165" s="44" t="s">
         <v>373</v>
       </c>
-      <c r="H165" s="46" t="s">
+      <c r="H165" s="45" t="s">
         <v>374</v>
       </c>
-      <c r="I165" s="39" t="s">
+      <c r="I165" s="46" t="s">
         <v>375</v>
       </c>
       <c r="J165" s="34" t="s">
@@ -10761,7 +10751,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="183" customFormat="false" ht="42.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="183" customFormat="false" ht="77.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="30" t="n">
         <v>468</v>
       </c>
@@ -10786,7 +10776,7 @@
       <c r="H183" s="49" t="s">
         <v>413</v>
       </c>
-      <c r="I183" s="50" t="s">
+      <c r="I183" s="44" t="s">
         <v>414</v>
       </c>
       <c r="J183" s="34" t="s">
@@ -10800,7 +10790,7 @@
       <c r="N183" s="34" t="s">
         <v>67</v>
       </c>
-      <c r="O183" s="51" t="s">
+      <c r="O183" s="50" t="s">
         <v>415</v>
       </c>
       <c r="P183" s="34" t="s">
@@ -10819,7 +10809,7 @@
         <v>71</v>
       </c>
       <c r="U183" s="30"/>
-      <c r="V183" s="52" t="s">
+      <c r="V183" s="51" t="s">
         <v>416</v>
       </c>
       <c r="W183" s="30" t="s">
@@ -11176,7 +11166,7 @@
       <c r="D193" s="30" t="s">
         <v>435</v>
       </c>
-      <c r="E193" s="53" t="s">
+      <c r="E193" s="52" t="s">
         <v>436</v>
       </c>
       <c r="F193" s="33"/>
@@ -15294,7 +15284,7 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="53" t="s">
         <v>444</v>
       </c>
       <c r="B1" s="19" t="s">
@@ -15306,158 +15296,158 @@
       <c r="D1" s="19" t="s">
         <v>446</v>
       </c>
-      <c r="F1" s="55" t="s">
+      <c r="F1" s="54" t="s">
         <v>447</v>
       </c>
-      <c r="G1" s="56" t="s">
+      <c r="G1" s="55" t="s">
         <v>448</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="56" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="57" t="s">
+      <c r="B2" s="56" t="s">
         <v>449</v>
       </c>
-      <c r="C2" s="58" t="s">
+      <c r="C2" s="57" t="s">
         <v>450</v>
       </c>
-      <c r="D2" s="59" t="s">
+      <c r="D2" s="58" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="57" t="s">
+      <c r="A3" s="56" t="s">
         <v>55</v>
       </c>
-      <c r="B3" s="57" t="s">
+      <c r="B3" s="56" t="s">
         <v>449</v>
       </c>
-      <c r="C3" s="58" t="s">
+      <c r="C3" s="57" t="s">
         <v>452</v>
       </c>
-      <c r="D3" s="59" t="s">
+      <c r="D3" s="58" t="s">
         <v>453</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="57" t="s">
+      <c r="A4" s="56" t="s">
         <v>59</v>
       </c>
-      <c r="B4" s="57" t="s">
+      <c r="B4" s="56" t="s">
         <v>449</v>
       </c>
-      <c r="C4" s="58" t="s">
+      <c r="C4" s="57" t="s">
         <v>454</v>
       </c>
-      <c r="D4" s="60" t="s">
+      <c r="D4" s="59" t="s">
         <v>455</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="57" t="s">
+      <c r="A5" s="56" t="s">
         <v>73</v>
       </c>
-      <c r="B5" s="57" t="s">
+      <c r="B5" s="56" t="s">
         <v>449</v>
       </c>
-      <c r="C5" s="58" t="s">
+      <c r="C5" s="57" t="s">
         <v>456</v>
       </c>
-      <c r="D5" s="59" t="s">
+      <c r="D5" s="58" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="57" t="s">
+      <c r="A6" s="56" t="s">
         <v>75</v>
       </c>
-      <c r="B6" s="57" t="s">
+      <c r="B6" s="56" t="s">
         <v>449</v>
       </c>
-      <c r="C6" s="58" t="s">
+      <c r="C6" s="57" t="s">
         <v>458</v>
       </c>
-      <c r="D6" s="60" t="s">
+      <c r="D6" s="59" t="s">
         <v>459</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="57" t="s">
+      <c r="A7" s="56" t="s">
         <v>77</v>
       </c>
-      <c r="B7" s="57" t="s">
+      <c r="B7" s="56" t="s">
         <v>449</v>
       </c>
-      <c r="C7" s="58" t="s">
+      <c r="C7" s="57" t="s">
         <v>460</v>
       </c>
-      <c r="D7" s="60" t="s">
+      <c r="D7" s="59" t="s">
         <v>461</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="57" t="s">
+      <c r="A8" s="56" t="s">
         <v>61</v>
       </c>
-      <c r="B8" s="57" t="s">
+      <c r="B8" s="56" t="s">
         <v>449</v>
       </c>
-      <c r="C8" s="58" t="s">
+      <c r="C8" s="57" t="s">
         <v>462</v>
       </c>
-      <c r="D8" s="60" t="s">
+      <c r="D8" s="59" t="s">
         <v>463</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="57" t="s">
+      <c r="A9" s="56" t="s">
         <v>57</v>
       </c>
-      <c r="B9" s="57" t="s">
+      <c r="B9" s="56" t="s">
         <v>449</v>
       </c>
-      <c r="C9" s="58" t="s">
+      <c r="C9" s="57" t="s">
         <v>464</v>
       </c>
-      <c r="D9" s="60" t="s">
+      <c r="D9" s="59" t="s">
         <v>465</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="57" t="s">
+      <c r="A10" s="56" t="s">
         <v>466</v>
       </c>
-      <c r="B10" s="57" t="s">
+      <c r="B10" s="56" t="s">
         <v>449</v>
       </c>
-      <c r="C10" s="61" t="s">
+      <c r="C10" s="60" t="s">
         <v>467</v>
       </c>
-      <c r="D10" s="59" t="s">
+      <c r="D10" s="58" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="57" t="s">
+      <c r="A11" s="56" t="s">
         <v>333</v>
       </c>
-      <c r="B11" s="57" t="s">
+      <c r="B11" s="56" t="s">
         <v>449</v>
       </c>
-      <c r="C11" s="58" t="s">
+      <c r="C11" s="57" t="s">
         <v>469</v>
       </c>
-      <c r="D11" s="60" t="s">
+      <c r="D11" s="59" t="s">
         <v>470</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D12" s="62"/>
+      <c r="D12" s="61"/>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="D13" s="62"/>
+      <c r="D13" s="61"/>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -16433,32 +16423,32 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="62" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="63" t="s">
+      <c r="B1" s="62" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="63" t="s">
+      <c r="A2" s="62" t="s">
         <v>71</v>
       </c>
-      <c r="B2" s="63" t="s">
+      <c r="B2" s="62" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="63" t="s">
+      <c r="A3" s="62" t="s">
         <v>471</v>
       </c>
-      <c r="B3" s="63" t="s">
+      <c r="B3" s="62" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="63"/>
-      <c r="B4" s="63"/>
+      <c r="A4" s="62"/>
+      <c r="B4" s="62"/>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>

--- a/GATEWAY/A1#111PASERCONSULTINGXX/PaSer_Consulting_Group/WinPreGest/1.0.0/accreditamento-checklist_V8.2.7.xlsx
+++ b/GATEWAY/A1#111PASERCONSULTINGXX/PaSer_Consulting_Group/WinPreGest/1.0.0/accreditamento-checklist_V8.2.7.xlsx
@@ -357,29 +357,29 @@
     <t xml:space="preserve">VALIDAZIONE_TOKEN_JWT_LDO_KO</t>
   </si>
   <si>
-    <t xml:space="preserve">PSS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_TOKEN_JWT_PSS_KO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_TOKEN_JWT_RAD_KO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RSA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDAZIONE_TOKEN_JWT_RSA_KO</t>
-  </si>
-  <si>
     <t xml:space="preserve">Precondizioni:
 Il fornitore utilizza un token jwt mancante di campi obbligatori, quindi non valido.
 Descrizione di Business del caso di test: 
 Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" con un token jwt non valido a causa della mancanza di uno o più campi obbligatori al fine di testare la gestione dell'errore sul token (status code 403), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway.
 Al fine di rendere non valido il token è necessario non valorizzare nel JWT il campo "purpose_of_use".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_TOKEN_JWT_PSS_KO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_TOKEN_JWT_RAD_KO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RSA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALIDAZIONE_TOKEN_JWT_RSA_KO</t>
   </si>
   <si>
     <t xml:space="preserve">2026-03-11T20:46:00Z</t>
@@ -1468,13 +1468,13 @@
 Il Documento CDA2 Referto Specialistica Ambulatoriale dovrà essere composto in modo da risultare valido dal punto di vista sintattico, semantico, terminologico. I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso dalla sezione "CASO DI TEST 24" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_OK" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-03-17T18:36:00Z </t>
-  </si>
-  <si>
-    <t xml:space="preserve">c3cb1790c985cf3429d83dfea84865c6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16.840.1.113883.2.9.2.9999.1.fa7401d4f3cfff0f43f763829522b91f1b908030881f8ed8262690caff2f096d.5b86d7a63f^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t xml:space="preserve">2026-03-30T16:43:00Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">68675291a96f5e7b5f378efd5f156726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16.840.1.113883.2.9.2.120.4.4.b10a87fc05b8f96b9a99348df3abeb7c94d60d74dd3dc6728ed3014edac6478c.11e358bca3^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t xml:space="preserve">Nessuna gestione errore richiesta – documento valido </t>
@@ -1490,13 +1490,13 @@
 Il Documento CDA2 Referto Specialistica Ambulatoriale dovrà essere composto in modo da risultare valido dal punto di vista sintattico, semantico, terminologico. I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso dalla sezione "CASO DI TEST 25" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_OK" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-03-17T18:55:00Z </t>
-  </si>
-  <si>
-    <t xml:space="preserve">42eb308576d775d29bbf70af68b8447d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16.840.1.113883.2.9.2.9999.1.fd8f5b9b9f88a84af08a1139870cecd7a69e70e991056b2d06d5c4709bebeec0.65b7e5771d^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t xml:space="preserve">2026-03-30T17:13:00Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7665b244a32e3b6aa9d82a76ebba560b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16.840.1.113883.2.9.2.120.4.4.c3d6f85dc61195d0310cfcfc39943fa2a9bd8001c3d319ae529b1d2e089163ee.4995a05f3d^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t xml:space="preserve">VALIDAZIONE_CDA2_LDO_CT17</t>
@@ -4224,7 +4224,7 @@
         <v>56</v>
       </c>
       <c r="E12" s="38" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F12" s="33"/>
       <c r="G12" s="33"/>
@@ -4255,10 +4255,10 @@
         <v>47</v>
       </c>
       <c r="C13" s="37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D13" s="30" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E13" s="38" t="s">
         <v>53</v>
@@ -4292,10 +4292,10 @@
         <v>47</v>
       </c>
       <c r="C14" s="37" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D14" s="30" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E14" s="38" t="s">
         <v>53</v>
@@ -4321,7 +4321,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="98.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="30" t="n">
         <v>32</v>
       </c>
@@ -4329,13 +4329,13 @@
         <v>47</v>
       </c>
       <c r="C15" s="37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D15" s="30" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E15" s="38" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F15" s="33" t="n">
         <v>46092</v>
@@ -4579,7 +4579,7 @@
         <v>47</v>
       </c>
       <c r="C21" s="37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D21" s="30" t="s">
         <v>82</v>
@@ -4616,7 +4616,7 @@
         <v>47</v>
       </c>
       <c r="C22" s="37" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D22" s="30" t="s">
         <v>83</v>
@@ -4645,7 +4645,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="98.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="30" t="n">
         <v>40</v>
       </c>
@@ -4653,7 +4653,7 @@
         <v>47</v>
       </c>
       <c r="C23" s="37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D23" s="30" t="s">
         <v>84</v>
@@ -4907,7 +4907,7 @@
         <v>47</v>
       </c>
       <c r="C29" s="37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D29" s="30" t="s">
         <v>96</v>
@@ -4946,7 +4946,7 @@
         <v>47</v>
       </c>
       <c r="C30" s="37" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D30" s="30" t="s">
         <v>97</v>
@@ -4977,7 +4977,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="66.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="30" t="n">
         <v>48</v>
       </c>
@@ -4985,7 +4985,7 @@
         <v>47</v>
       </c>
       <c r="C31" s="37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D31" s="30" t="s">
         <v>98</v>
@@ -5833,7 +5833,7 @@
         <v>47</v>
       </c>
       <c r="C53" s="37" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D53" s="30" t="s">
         <v>142</v>
@@ -5870,7 +5870,7 @@
         <v>47</v>
       </c>
       <c r="C54" s="37" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D54" s="30" t="s">
         <v>144</v>
@@ -5907,7 +5907,7 @@
         <v>47</v>
       </c>
       <c r="C55" s="37" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D55" s="30" t="s">
         <v>146</v>
@@ -5944,7 +5944,7 @@
         <v>47</v>
       </c>
       <c r="C56" s="37" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D56" s="30" t="s">
         <v>148</v>
@@ -5981,7 +5981,7 @@
         <v>47</v>
       </c>
       <c r="C57" s="37" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D57" s="30" t="s">
         <v>150</v>
@@ -6018,7 +6018,7 @@
         <v>47</v>
       </c>
       <c r="C58" s="37" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D58" s="30" t="s">
         <v>152</v>
@@ -6055,7 +6055,7 @@
         <v>47</v>
       </c>
       <c r="C59" s="37" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D59" s="30" t="s">
         <v>154</v>
@@ -6092,7 +6092,7 @@
         <v>47</v>
       </c>
       <c r="C60" s="37" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D60" s="30" t="s">
         <v>156</v>
@@ -6129,7 +6129,7 @@
         <v>47</v>
       </c>
       <c r="C61" s="37" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D61" s="30" t="s">
         <v>158</v>
@@ -6166,7 +6166,7 @@
         <v>47</v>
       </c>
       <c r="C62" s="37" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D62" s="30" t="s">
         <v>160</v>
@@ -6203,7 +6203,7 @@
         <v>47</v>
       </c>
       <c r="C63" s="37" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D63" s="30" t="s">
         <v>162</v>
@@ -6240,7 +6240,7 @@
         <v>47</v>
       </c>
       <c r="C64" s="37" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D64" s="30" t="s">
         <v>164</v>
@@ -6277,7 +6277,7 @@
         <v>47</v>
       </c>
       <c r="C65" s="37" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D65" s="30" t="s">
         <v>166</v>
@@ -6314,7 +6314,7 @@
         <v>47</v>
       </c>
       <c r="C66" s="37" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D66" s="30" t="s">
         <v>168</v>
@@ -6351,7 +6351,7 @@
         <v>47</v>
       </c>
       <c r="C67" s="37" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D67" s="30" t="s">
         <v>170</v>
@@ -6388,7 +6388,7 @@
         <v>47</v>
       </c>
       <c r="C68" s="37" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D68" s="30" t="s">
         <v>172</v>
@@ -8164,7 +8164,7 @@
         <v>47</v>
       </c>
       <c r="C116" s="37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D116" s="30" t="s">
         <v>268</v>
@@ -8205,7 +8205,7 @@
         <v>47</v>
       </c>
       <c r="C117" s="37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D117" s="30" t="s">
         <v>271</v>
@@ -8246,7 +8246,7 @@
         <v>47</v>
       </c>
       <c r="C118" s="37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D118" s="30" t="s">
         <v>273</v>
@@ -8287,7 +8287,7 @@
         <v>47</v>
       </c>
       <c r="C119" s="37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D119" s="30" t="s">
         <v>275</v>
@@ -8328,7 +8328,7 @@
         <v>47</v>
       </c>
       <c r="C120" s="37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D120" s="30" t="s">
         <v>277</v>
@@ -8369,7 +8369,7 @@
         <v>47</v>
       </c>
       <c r="C121" s="37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D121" s="30" t="s">
         <v>279</v>
@@ -8410,7 +8410,7 @@
         <v>47</v>
       </c>
       <c r="C122" s="37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D122" s="30" t="s">
         <v>281</v>
@@ -8451,7 +8451,7 @@
         <v>47</v>
       </c>
       <c r="C123" s="37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D123" s="30" t="s">
         <v>283</v>
@@ -8492,7 +8492,7 @@
         <v>47</v>
       </c>
       <c r="C124" s="37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D124" s="30" t="s">
         <v>285</v>
@@ -8533,7 +8533,7 @@
         <v>47</v>
       </c>
       <c r="C125" s="37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D125" s="30" t="s">
         <v>287</v>
@@ -8574,7 +8574,7 @@
         <v>47</v>
       </c>
       <c r="C126" s="37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D126" s="30" t="s">
         <v>289</v>
@@ -8615,7 +8615,7 @@
         <v>47</v>
       </c>
       <c r="C127" s="37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D127" s="30" t="s">
         <v>291</v>
@@ -8656,7 +8656,7 @@
         <v>47</v>
       </c>
       <c r="C128" s="37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D128" s="30" t="s">
         <v>293</v>
@@ -8697,7 +8697,7 @@
         <v>47</v>
       </c>
       <c r="C129" s="37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D129" s="30" t="s">
         <v>295</v>
@@ -8738,7 +8738,7 @@
         <v>47</v>
       </c>
       <c r="C130" s="37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D130" s="30" t="s">
         <v>297</v>
@@ -8779,7 +8779,7 @@
         <v>47</v>
       </c>
       <c r="C131" s="37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D131" s="30" t="s">
         <v>299</v>
@@ -8816,7 +8816,7 @@
         <v>47</v>
       </c>
       <c r="C132" s="37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D132" s="30" t="s">
         <v>301</v>
@@ -8853,7 +8853,7 @@
         <v>47</v>
       </c>
       <c r="C133" s="37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D133" s="30" t="s">
         <v>303</v>
@@ -8890,7 +8890,7 @@
         <v>47</v>
       </c>
       <c r="C134" s="37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D134" s="30" t="s">
         <v>305</v>
@@ -8927,7 +8927,7 @@
         <v>47</v>
       </c>
       <c r="C135" s="37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D135" s="30" t="s">
         <v>307</v>
@@ -8964,7 +8964,7 @@
         <v>47</v>
       </c>
       <c r="C136" s="37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D136" s="30" t="s">
         <v>309</v>
@@ -9001,7 +9001,7 @@
         <v>47</v>
       </c>
       <c r="C137" s="37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D137" s="30" t="s">
         <v>311</v>
@@ -9038,7 +9038,7 @@
         <v>47</v>
       </c>
       <c r="C138" s="37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D138" s="30" t="s">
         <v>313</v>
@@ -9075,7 +9075,7 @@
         <v>47</v>
       </c>
       <c r="C139" s="37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D139" s="30" t="s">
         <v>315</v>
@@ -9112,7 +9112,7 @@
         <v>47</v>
       </c>
       <c r="C140" s="37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D140" s="30" t="s">
         <v>317</v>
@@ -9149,7 +9149,7 @@
         <v>47</v>
       </c>
       <c r="C141" s="37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D141" s="30" t="s">
         <v>319</v>
@@ -9186,7 +9186,7 @@
         <v>47</v>
       </c>
       <c r="C142" s="37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D142" s="30" t="s">
         <v>321</v>
@@ -9223,7 +9223,7 @@
         <v>47</v>
       </c>
       <c r="C143" s="37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D143" s="30" t="s">
         <v>323</v>
@@ -9260,7 +9260,7 @@
         <v>47</v>
       </c>
       <c r="C144" s="37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D144" s="30" t="s">
         <v>325</v>
@@ -9297,7 +9297,7 @@
         <v>47</v>
       </c>
       <c r="C145" s="37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D145" s="30" t="s">
         <v>327</v>
@@ -10000,7 +10000,7 @@
         <v>47</v>
       </c>
       <c r="C164" s="37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D164" s="30" t="s">
         <v>364</v>
@@ -10009,7 +10009,7 @@
         <v>365</v>
       </c>
       <c r="F164" s="33" t="n">
-        <v>46098</v>
+        <v>46111</v>
       </c>
       <c r="G164" s="44" t="s">
         <v>366</v>
@@ -10055,7 +10055,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="165" customFormat="false" ht="87.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="30" t="n">
         <v>449</v>
       </c>
@@ -10063,7 +10063,7 @@
         <v>47</v>
       </c>
       <c r="C165" s="37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D165" s="30" t="s">
         <v>371</v>
@@ -10072,7 +10072,7 @@
         <v>372</v>
       </c>
       <c r="F165" s="33" t="n">
-        <v>46098</v>
+        <v>46111</v>
       </c>
       <c r="G165" s="44" t="s">
         <v>373</v>
@@ -10496,7 +10496,7 @@
         <v>47</v>
       </c>
       <c r="C176" s="37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D176" s="30" t="s">
         <v>396</v>
@@ -10537,7 +10537,7 @@
         <v>47</v>
       </c>
       <c r="C177" s="37" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D177" s="30" t="s">
         <v>398</v>
@@ -10751,7 +10751,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="183" customFormat="false" ht="77.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="183" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="30" t="n">
         <v>468</v>
       </c>
@@ -10759,7 +10759,7 @@
         <v>47</v>
       </c>
       <c r="C183" s="37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D183" s="30" t="s">
         <v>410</v>
@@ -10824,7 +10824,7 @@
         <v>47</v>
       </c>
       <c r="C184" s="37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D184" s="30" t="s">
         <v>417</v>
@@ -10898,7 +10898,7 @@
         <v>47</v>
       </c>
       <c r="C186" s="37" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D186" s="30" t="s">
         <v>421</v>
@@ -10935,7 +10935,7 @@
         <v>47</v>
       </c>
       <c r="C187" s="37" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D187" s="30" t="s">
         <v>423</v>
@@ -11009,7 +11009,7 @@
         <v>47</v>
       </c>
       <c r="C189" s="37" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D189" s="30" t="s">
         <v>427</v>
@@ -11046,7 +11046,7 @@
         <v>47</v>
       </c>
       <c r="C190" s="37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D190" s="30" t="s">
         <v>429</v>
@@ -11087,7 +11087,7 @@
         <v>47</v>
       </c>
       <c r="C191" s="37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D191" s="30" t="s">
         <v>431</v>
@@ -11124,7 +11124,7 @@
         <v>47</v>
       </c>
       <c r="C192" s="37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D192" s="30" t="s">
         <v>433</v>
@@ -11161,7 +11161,7 @@
         <v>47</v>
       </c>
       <c r="C193" s="37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D193" s="30" t="s">
         <v>435</v>
@@ -15333,7 +15333,7 @@
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="56" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B4" s="56" t="s">
         <v>449</v>
@@ -15389,7 +15389,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="56" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B8" s="56" t="s">
         <v>449</v>
@@ -15403,7 +15403,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="56" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B9" s="56" t="s">
         <v>449</v>

--- a/GATEWAY/A1#111PASERCONSULTINGXX/PaSer_Consulting_Group/WinPreGest/1.0.0/accreditamento-checklist_V8.2.7.xlsx
+++ b/GATEWAY/A1#111PASERCONSULTINGXX/PaSer_Consulting_Group/WinPreGest/1.0.0/accreditamento-checklist_V8.2.7.xlsx
@@ -1468,13 +1468,13 @@
 Il Documento CDA2 Referto Specialistica Ambulatoriale dovrà essere composto in modo da risultare valido dal punto di vista sintattico, semantico, terminologico. I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso dalla sezione "CASO DI TEST 24" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_OK" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-03-30T16:43:00Z</t>
-  </si>
-  <si>
-    <t xml:space="preserve">68675291a96f5e7b5f378efd5f156726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16.840.1.113883.2.9.2.120.4.4.b10a87fc05b8f96b9a99348df3abeb7c94d60d74dd3dc6728ed3014edac6478c.11e358bca3^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t xml:space="preserve">2026-03-31T19:46:00Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">373f6d8cfc5db943567c4071860ab334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16.840.1.113883.2.9.2.120.4.4.821307df0168cbee0ccfa87dac22e1d8b021c399b67cc870b35be9f25ce8d922.deb7a019c0^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t xml:space="preserve">Nessuna gestione errore richiesta – documento valido </t>
@@ -1490,13 +1490,13 @@
 Il Documento CDA2 Referto Specialistica Ambulatoriale dovrà essere composto in modo da risultare valido dal punto di vista sintattico, semantico, terminologico. I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso dalla sezione "CASO DI TEST 25" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_OK" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-03-30T17:13:00Z</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7665b244a32e3b6aa9d82a76ebba560b</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16.840.1.113883.2.9.2.120.4.4.c3d6f85dc61195d0310cfcfc39943fa2a9bd8001c3d319ae529b1d2e089163ee.4995a05f3d^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t xml:space="preserve">2026-03-30T19:49:00Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8148d2d7e2e27c4cf534e80bc4d37d76</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16.840.1.113883.2.9.2.120.4.4.b1ee57f312792282524ad52358c2cf19f74af40ff47dd9431117b3bffdf697c2.1fa5b82900^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t xml:space="preserve">VALIDAZIONE_CDA2_LDO_CT17</t>
@@ -4261,7 +4261,7 @@
         <v>59</v>
       </c>
       <c r="E13" s="38" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F13" s="33"/>
       <c r="G13" s="33"/>
@@ -10009,7 +10009,7 @@
         <v>365</v>
       </c>
       <c r="F164" s="33" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="G164" s="44" t="s">
         <v>366</v>
@@ -10072,7 +10072,7 @@
         <v>372</v>
       </c>
       <c r="F165" s="33" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="G165" s="44" t="s">
         <v>373</v>

--- a/GATEWAY/A1#111PASERCONSULTINGXX/PaSer_Consulting_Group/WinPreGest/1.0.0/accreditamento-checklist_V8.2.7.xlsx
+++ b/GATEWAY/A1#111PASERCONSULTINGXX/PaSer_Consulting_Group/WinPreGest/1.0.0/accreditamento-checklist_V8.2.7.xlsx
@@ -1490,13 +1490,13 @@
 Il Documento CDA2 Referto Specialistica Ambulatoriale dovrà essere composto in modo da risultare valido dal punto di vista sintattico, semantico, terminologico. I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso dalla sezione "CASO DI TEST 25" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_OK" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-03-30T19:49:00Z</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8148d2d7e2e27c4cf534e80bc4d37d76</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16.840.1.113883.2.9.2.120.4.4.b1ee57f312792282524ad52358c2cf19f74af40ff47dd9431117b3bffdf697c2.1fa5b82900^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t xml:space="preserve">2026-04-01T18:44:00Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">00ec123fe5010ab985bc5105fd88ef96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16.840.1.113883.2.9.2.120.4.4.22d62bb26d5902fb90bc1fdc0c730994b60002d3384fbe9c201c820f4b27049f.b593e8a85f^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t xml:space="preserve">VALIDAZIONE_CDA2_LDO_CT17</t>
@@ -4298,7 +4298,7 @@
         <v>61</v>
       </c>
       <c r="E14" s="38" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F14" s="33"/>
       <c r="G14" s="33"/>
@@ -10072,7 +10072,7 @@
         <v>372</v>
       </c>
       <c r="F165" s="33" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="G165" s="44" t="s">
         <v>373</v>

--- a/GATEWAY/A1#111PASERCONSULTINGXX/PaSer_Consulting_Group/WinPreGest/1.0.0/accreditamento-checklist_V8.2.7.xlsx
+++ b/GATEWAY/A1#111PASERCONSULTINGXX/PaSer_Consulting_Group/WinPreGest/1.0.0/accreditamento-checklist_V8.2.7.xlsx
@@ -1490,13 +1490,13 @@
 Il Documento CDA2 Referto Specialistica Ambulatoriale dovrà essere composto in modo da risultare valido dal punto di vista sintattico, semantico, terminologico. I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso dalla sezione "CASO DI TEST 25" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_OK" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-04-01T18:44:00Z</t>
-  </si>
-  <si>
-    <t xml:space="preserve">00ec123fe5010ab985bc5105fd88ef96</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16.840.1.113883.2.9.2.120.4.4.22d62bb26d5902fb90bc1fdc0c730994b60002d3384fbe9c201c820f4b27049f.b593e8a85f^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t xml:space="preserve">2026-04-07T18:23:00Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e84b6a48bfdeea210e2bcb6c73164641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16.840.1.113883.2.9.2.120.4.4.a4a8ba1c417300da8acea2f010cce59be1eb7262af663b38e55bf05b5b0d8369.359c2d8cd6^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t xml:space="preserve">VALIDAZIONE_CDA2_LDO_CT17</t>
@@ -10072,7 +10072,7 @@
         <v>372</v>
       </c>
       <c r="F165" s="33" t="n">
-        <v>46113</v>
+        <v>46119</v>
       </c>
       <c r="G165" s="44" t="s">
         <v>373</v>

--- a/GATEWAY/A1#111PASERCONSULTINGXX/PaSer_Consulting_Group/WinPreGest/1.0.0/accreditamento-checklist_V8.2.7.xlsx
+++ b/GATEWAY/A1#111PASERCONSULTINGXX/PaSer_Consulting_Group/WinPreGest/1.0.0/accreditamento-checklist_V8.2.7.xlsx
@@ -1490,13 +1490,13 @@
 Il Documento CDA2 Referto Specialistica Ambulatoriale dovrà essere composto in modo da risultare valido dal punto di vista sintattico, semantico, terminologico. I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso dalla sezione "CASO DI TEST 25" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_OK" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-04-07T18:23:00Z</t>
-  </si>
-  <si>
-    <t xml:space="preserve">e84b6a48bfdeea210e2bcb6c73164641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16.840.1.113883.2.9.2.120.4.4.a4a8ba1c417300da8acea2f010cce59be1eb7262af663b38e55bf05b5b0d8369.359c2d8cd6^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t xml:space="preserve">2026-04-08T16:59:00Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cfc027feb664c7fb77bd5a8343458bb0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16.840.1.113883.2.9.2.120.4.4.a4a8ba1c417300da8acea2f010cce59be1eb7262af663b38e55bf05b5b0d8369.edef6bd902^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t xml:space="preserve">VALIDAZIONE_CDA2_LDO_CT17</t>
@@ -10072,7 +10072,7 @@
         <v>372</v>
       </c>
       <c r="F165" s="33" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="G165" s="44" t="s">
         <v>373</v>

--- a/GATEWAY/A1#111PASERCONSULTINGXX/PaSer_Consulting_Group/WinPreGest/1.0.0/accreditamento-checklist_V8.2.7.xlsx
+++ b/GATEWAY/A1#111PASERCONSULTINGXX/PaSer_Consulting_Group/WinPreGest/1.0.0/accreditamento-checklist_V8.2.7.xlsx
@@ -1490,13 +1490,13 @@
 Il Documento CDA2 Referto Specialistica Ambulatoriale dovrà essere composto in modo da risultare valido dal punto di vista sintattico, semantico, terminologico. I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso dalla sezione "CASO DI TEST 25" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_OK" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-04-08T16:59:00Z</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cfc027feb664c7fb77bd5a8343458bb0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16.840.1.113883.2.9.2.120.4.4.a4a8ba1c417300da8acea2f010cce59be1eb7262af663b38e55bf05b5b0d8369.edef6bd902^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t xml:space="preserve">2026-04-08T19:17:00Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6735929b9609d18f7f3ac4f4f5984085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16.840.1.113883.2.9.2.120.4.4.6a8dbb2840630370c47e39cc18f360a6899b8a90652c28f12b488833683593bc.ecac843f78^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t xml:space="preserve">VALIDAZIONE_CDA2_LDO_CT17</t>

--- a/GATEWAY/A1#111PASERCONSULTINGXX/PaSer_Consulting_Group/WinPreGest/1.0.0/accreditamento-checklist_V8.2.7.xlsx
+++ b/GATEWAY/A1#111PASERCONSULTINGXX/PaSer_Consulting_Group/WinPreGest/1.0.0/accreditamento-checklist_V8.2.7.xlsx
@@ -1490,13 +1490,13 @@
 Il Documento CDA2 Referto Specialistica Ambulatoriale dovrà essere composto in modo da risultare valido dal punto di vista sintattico, semantico, terminologico. I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso dalla sezione "CASO DI TEST 25" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_OK" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-04-08T19:17:00Z</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6735929b9609d18f7f3ac4f4f5984085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16.840.1.113883.2.9.2.120.4.4.6a8dbb2840630370c47e39cc18f360a6899b8a90652c28f12b488833683593bc.ecac843f78^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t xml:space="preserve">2026-04-10T18:06:00Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14b46c3fdd481b6390be470764948751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16.840.1.113883.2.9.2.120.4.4.f7e0cf0a74e8fb5080f982b055b5b9bd087b808f8ec1ccc6c46f2a4be4833e5f.e6987bd574^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t xml:space="preserve">VALIDAZIONE_CDA2_LDO_CT17</t>
@@ -10072,7 +10072,7 @@
         <v>372</v>
       </c>
       <c r="F165" s="33" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="G165" s="44" t="s">
         <v>373</v>
